--- a/E/DJM02N.xlsx
+++ b/E/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="464">
   <si>
     <t/>
   </si>
@@ -187,6 +187,18 @@
     <t>TWIZZ TROP.CRSH 20'S</t>
   </si>
   <si>
+    <t>20113074</t>
+  </si>
+  <si>
+    <t>MARLBORO KRETEK 12'S</t>
+  </si>
+  <si>
+    <t>20122038</t>
+  </si>
+  <si>
+    <t>MRLBORO KRT BIRU 12S</t>
+  </si>
+  <si>
     <t>10010094</t>
   </si>
   <si>
@@ -253,31 +265,31 @@
     <t>MAGNUM 234 12S</t>
   </si>
   <si>
-    <t>20113074</t>
-  </si>
-  <si>
-    <t>MARLBORO KRETEK 12'S</t>
-  </si>
-  <si>
-    <t>20122038</t>
-  </si>
-  <si>
-    <t>MRLBORO KRT BIRU 12S</t>
-  </si>
-  <si>
     <t>20132342</t>
   </si>
   <si>
     <t>DJI SAM SOE MAESTR12</t>
   </si>
   <si>
+    <t>20134530</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE SP.PRM16</t>
+  </si>
+  <si>
+    <t>20125676</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE MG BIN12</t>
+  </si>
+  <si>
     <t>14</t>
   </si>
   <si>
-    <t>20134530</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE SP.PRM16</t>
+    <t>10030733</t>
+  </si>
+  <si>
+    <t>DJI SAM SOE S/PRM</t>
   </si>
   <si>
     <t>15</t>
@@ -331,18 +343,6 @@
     <t>FILTER MOTION 20'S</t>
   </si>
   <si>
-    <t>20125676</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE MG BIN12</t>
-  </si>
-  <si>
-    <t>10030733</t>
-  </si>
-  <si>
-    <t>DJI SAM SOE S/PRM</t>
-  </si>
-  <si>
     <t>20123283</t>
   </si>
   <si>
@@ -526,6 +526,12 @@
     <t>T/M FLTR COOL BRY16</t>
   </si>
   <si>
+    <t>20140141</t>
+  </si>
+  <si>
+    <t>DJARUM ROK.D WRP 12S</t>
+  </si>
+  <si>
     <t>20084820</t>
   </si>
   <si>
@@ -730,6 +736,18 @@
     <t>JAZY RK POPPIN16'S</t>
   </si>
   <si>
+    <t>20131551</t>
+  </si>
+  <si>
+    <t>JAZY KRETEK 12'S</t>
+  </si>
+  <si>
+    <t>20142823</t>
+  </si>
+  <si>
+    <t>JAZY MAX FILTER 12'S</t>
+  </si>
+  <si>
     <t>20095233</t>
   </si>
   <si>
@@ -1109,6 +1127,12 @@
   </si>
   <si>
     <t>CAMEL ICE LIME 16S</t>
+  </si>
+  <si>
+    <t>20143273</t>
+  </si>
+  <si>
+    <t>CAMEL KRETK KLSK 10S</t>
   </si>
   <si>
     <t>20130571</t>
@@ -1771,7 +1795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F217"/>
+  <dimension ref="A1:F221"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2212,10 +2236,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -2232,10 +2256,10 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2255,10 +2279,10 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2275,7 +2299,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2295,10 +2319,10 @@
         <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2315,10 +2339,10 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2335,7 +2359,7 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2355,10 +2379,10 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2375,7 +2399,7 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2395,7 +2419,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2415,10 +2439,10 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2435,7 +2459,7 @@
         <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2455,10 +2479,10 @@
         <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2475,7 +2499,7 @@
         <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2483,10 +2507,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2495,7 +2519,7 @@
         <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2503,19 +2527,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2523,22 +2547,22 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2555,10 +2579,10 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2575,7 +2599,7 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2595,10 +2619,10 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2615,10 +2639,10 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2635,10 +2659,10 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2655,7 +2679,7 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>9</v>
@@ -2675,10 +2699,10 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2695,10 +2719,10 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2775,7 +2799,7 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2795,7 +2819,7 @@
         <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -3075,7 +3099,7 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3095,7 +3119,7 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3312,10 +3336,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3335,7 +3359,7 @@
         <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3355,7 +3379,7 @@
         <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3375,7 +3399,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3395,7 +3419,7 @@
         <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3415,7 +3439,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3435,7 +3459,7 @@
         <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3455,7 +3479,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3475,7 +3499,7 @@
         <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3495,7 +3519,7 @@
         <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3515,7 +3539,7 @@
         <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3535,7 +3559,7 @@
         <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3555,7 +3579,7 @@
         <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3575,7 +3599,7 @@
         <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3592,10 +3616,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3615,7 +3639,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3635,7 +3659,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3655,7 +3679,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3675,7 +3699,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3695,7 +3719,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3715,10 +3739,10 @@
         <v>27</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3735,10 +3759,10 @@
         <v>27</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3755,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3775,7 +3799,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3792,10 +3816,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3815,7 +3839,7 @@
         <v>30</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3835,7 +3859,7 @@
         <v>30</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3855,7 +3879,7 @@
         <v>30</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3875,7 +3899,7 @@
         <v>30</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3895,7 +3919,7 @@
         <v>30</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3915,7 +3939,7 @@
         <v>30</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3935,7 +3959,7 @@
         <v>30</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3955,7 +3979,7 @@
         <v>30</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3975,7 +3999,7 @@
         <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3995,7 +4019,7 @@
         <v>30</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4015,10 +4039,10 @@
         <v>30</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4035,7 +4059,7 @@
         <v>30</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>245</v>
+        <v>42</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4043,10 +4067,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -4055,18 +4079,18 @@
         <v>30</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>248</v>
+        <v>90</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -4075,27 +4099,27 @@
         <v>30</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>251</v>
+        <v>93</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>251</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4103,42 +4127,42 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4195,7 +4219,7 @@
         <v>33</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4215,7 +4239,7 @@
         <v>33</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4235,7 +4259,7 @@
         <v>33</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4255,7 +4279,7 @@
         <v>33</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4275,7 +4299,7 @@
         <v>33</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4295,7 +4319,7 @@
         <v>33</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4318,7 +4342,7 @@
         <v>12</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4335,7 +4359,7 @@
         <v>33</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4355,7 +4379,7 @@
         <v>33</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4375,10 +4399,10 @@
         <v>33</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4418,7 +4442,7 @@
         <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4475,10 +4499,10 @@
         <v>33</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4495,7 +4519,7 @@
         <v>33</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4515,7 +4539,7 @@
         <v>33</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4538,7 +4562,7 @@
         <v>18</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4558,7 +4582,7 @@
         <v>18</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4578,7 +4602,7 @@
         <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4598,7 +4622,7 @@
         <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4618,7 +4642,7 @@
         <v>18</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4638,7 +4662,7 @@
         <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4718,7 +4742,7 @@
         <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4758,7 +4782,7 @@
         <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4795,10 +4819,10 @@
         <v>33</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4815,7 +4839,7 @@
         <v>33</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>9</v>
@@ -4835,7 +4859,7 @@
         <v>33</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>9</v>
@@ -4878,7 +4902,7 @@
         <v>21</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4898,7 +4922,7 @@
         <v>21</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4918,7 +4942,7 @@
         <v>21</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4955,7 +4979,7 @@
         <v>33</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4972,10 +4996,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4992,10 +5016,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -5012,10 +5036,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5035,7 +5059,7 @@
         <v>36</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5055,7 +5079,7 @@
         <v>36</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5075,7 +5099,7 @@
         <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5095,7 +5119,7 @@
         <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5115,7 +5139,7 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5135,7 +5159,7 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5155,7 +5179,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5175,10 +5199,10 @@
         <v>36</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5195,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5215,10 +5239,10 @@
         <v>36</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5232,13 +5256,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5252,10 +5276,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5272,13 +5296,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5292,10 +5316,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5315,7 +5339,7 @@
         <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5335,7 +5359,7 @@
         <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5355,7 +5379,7 @@
         <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5375,7 +5399,7 @@
         <v>39</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5395,7 +5419,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5415,7 +5439,7 @@
         <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5435,7 +5459,7 @@
         <v>39</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5455,7 +5479,7 @@
         <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5475,7 +5499,7 @@
         <v>39</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5495,7 +5519,7 @@
         <v>39</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5512,10 +5536,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5532,10 +5556,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5552,10 +5576,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5572,10 +5596,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5595,7 +5619,7 @@
         <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5615,10 +5639,10 @@
         <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5635,10 +5659,10 @@
         <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5655,10 +5679,10 @@
         <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5675,7 +5699,7 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5695,10 +5719,10 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5715,10 +5739,10 @@
         <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5735,10 +5759,10 @@
         <v>42</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5755,7 +5779,7 @@
         <v>42</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5775,7 +5799,7 @@
         <v>42</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5795,7 +5819,7 @@
         <v>42</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5812,10 +5836,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5832,10 +5856,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5852,10 +5876,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5872,10 +5896,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5892,10 +5916,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5912,10 +5936,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5932,10 +5956,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5952,10 +5976,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5972,10 +5996,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -5992,10 +6016,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6012,10 +6036,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6032,10 +6056,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6052,10 +6076,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6072,10 +6096,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6092,10 +6116,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6112,12 +6136,92 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E217" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E221" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F217" s="1" t="s">
+      <c r="F221" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/DJM02N.xlsx
+++ b/E/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="472">
   <si>
     <t/>
   </si>
@@ -343,6 +343,18 @@
     <t>FILTER MOTION 20'S</t>
   </si>
   <si>
+    <t>20143381</t>
+  </si>
+  <si>
+    <t>MARLBORO RED ADV20S</t>
+  </si>
+  <si>
+    <t>20143380</t>
+  </si>
+  <si>
+    <t>MARLBORO GOLD ADV20S</t>
+  </si>
+  <si>
     <t>20123283</t>
   </si>
   <si>
@@ -899,6 +911,18 @@
   </si>
   <si>
     <t>BLENDS TROPICAL 20'S</t>
+  </si>
+  <si>
+    <t>20143379</t>
+  </si>
+  <si>
+    <t>BLENDS  WTRMLN MIX20</t>
+  </si>
+  <si>
+    <t>20143382</t>
+  </si>
+  <si>
+    <t>BLENDS PASS FRTMIX20</t>
   </si>
   <si>
     <t>20135189</t>
@@ -1795,7 +1819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F221"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2739,18 +2763,18 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2759,18 +2783,18 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2779,10 +2803,10 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2799,10 +2823,10 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2819,10 +2843,10 @@
         <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2836,10 +2860,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2856,13 +2880,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2879,7 +2903,7 @@
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2899,10 +2923,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2919,7 +2943,7 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2939,7 +2963,7 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2959,7 +2983,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2979,7 +3003,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2999,10 +3023,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3019,10 +3043,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3039,10 +3063,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3059,10 +3083,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3079,7 +3103,7 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3099,7 +3123,7 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3119,7 +3143,7 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3136,10 +3160,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3156,10 +3180,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3179,7 +3203,7 @@
         <v>21</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -3199,7 +3223,7 @@
         <v>21</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -3219,7 +3243,7 @@
         <v>21</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3239,7 +3263,7 @@
         <v>21</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3259,7 +3283,7 @@
         <v>21</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3279,7 +3303,7 @@
         <v>21</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3299,7 +3323,7 @@
         <v>21</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3319,7 +3343,7 @@
         <v>21</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3339,7 +3363,7 @@
         <v>21</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3356,10 +3380,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3376,10 +3400,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3399,7 +3423,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3419,7 +3443,7 @@
         <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3439,7 +3463,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3459,7 +3483,7 @@
         <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3479,7 +3503,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3499,7 +3523,7 @@
         <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3519,7 +3543,7 @@
         <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3539,7 +3563,7 @@
         <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3559,7 +3583,7 @@
         <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3579,7 +3603,7 @@
         <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3599,7 +3623,7 @@
         <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3619,7 +3643,7 @@
         <v>24</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3636,10 +3660,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3656,10 +3680,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3679,7 +3703,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3699,7 +3723,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3719,7 +3743,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3739,7 +3763,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3759,10 +3783,10 @@
         <v>27</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3779,7 +3803,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3799,10 +3823,10 @@
         <v>27</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3819,7 +3843,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3836,10 +3860,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3856,10 +3880,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3879,7 +3903,7 @@
         <v>30</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3899,7 +3923,7 @@
         <v>30</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3919,7 +3943,7 @@
         <v>30</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3939,7 +3963,7 @@
         <v>30</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3959,7 +3983,7 @@
         <v>30</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3979,7 +4003,7 @@
         <v>30</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3999,7 +4023,7 @@
         <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4019,7 +4043,7 @@
         <v>30</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4039,7 +4063,7 @@
         <v>30</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4059,7 +4083,7 @@
         <v>30</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4079,7 +4103,7 @@
         <v>30</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4099,10 +4123,10 @@
         <v>30</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4119,7 +4143,7 @@
         <v>30</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>251</v>
+        <v>90</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4127,10 +4151,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -4139,18 +4163,18 @@
         <v>30</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>254</v>
+        <v>93</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -4159,50 +4183,50 @@
         <v>30</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4279,7 +4303,7 @@
         <v>33</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4299,7 +4323,7 @@
         <v>33</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4339,7 +4363,7 @@
         <v>33</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4359,7 +4383,7 @@
         <v>33</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4402,7 +4426,7 @@
         <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4419,7 +4443,7 @@
         <v>33</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4439,10 +4463,10 @@
         <v>33</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4502,7 +4526,7 @@
         <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4542,7 +4566,7 @@
         <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4559,7 +4583,7 @@
         <v>33</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4579,7 +4603,7 @@
         <v>33</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4599,10 +4623,10 @@
         <v>33</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4619,7 +4643,7 @@
         <v>33</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>9</v>
@@ -4642,7 +4666,7 @@
         <v>18</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4662,7 +4686,7 @@
         <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4702,7 +4726,7 @@
         <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4722,7 +4746,7 @@
         <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4742,7 +4766,7 @@
         <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4802,7 +4826,7 @@
         <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4842,7 +4866,7 @@
         <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4862,7 +4886,7 @@
         <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4879,7 +4903,7 @@
         <v>33</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>9</v>
@@ -4899,10 +4923,10 @@
         <v>33</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4919,7 +4943,7 @@
         <v>33</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>9</v>
@@ -4939,7 +4963,7 @@
         <v>33</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>9</v>
@@ -4962,7 +4986,7 @@
         <v>21</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4982,7 +5006,7 @@
         <v>21</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5002,7 +5026,7 @@
         <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5022,7 +5046,7 @@
         <v>21</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5039,7 +5063,7 @@
         <v>33</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -5056,10 +5080,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -5076,10 +5100,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5096,10 +5120,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5116,10 +5140,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5139,7 +5163,7 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5159,7 +5183,7 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5179,7 +5203,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5199,7 +5223,7 @@
         <v>36</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5219,7 +5243,7 @@
         <v>36</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5239,7 +5263,7 @@
         <v>36</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5259,10 +5283,10 @@
         <v>36</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5279,7 +5303,7 @@
         <v>36</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5299,10 +5323,10 @@
         <v>36</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5319,7 +5343,7 @@
         <v>36</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5336,13 +5360,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5356,10 +5380,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5376,13 +5400,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5396,10 +5420,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5419,7 +5443,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5439,7 +5463,7 @@
         <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5459,7 +5483,7 @@
         <v>39</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5479,7 +5503,7 @@
         <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5499,7 +5523,7 @@
         <v>39</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5519,7 +5543,7 @@
         <v>39</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5539,7 +5563,7 @@
         <v>39</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5559,7 +5583,7 @@
         <v>39</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5579,7 +5603,7 @@
         <v>39</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5599,7 +5623,7 @@
         <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5616,10 +5640,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5636,10 +5660,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5656,10 +5680,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5676,10 +5700,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5699,7 +5723,7 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5719,10 +5743,10 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5739,10 +5763,10 @@
         <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5759,10 +5783,10 @@
         <v>42</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5779,7 +5803,7 @@
         <v>42</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5799,10 +5823,10 @@
         <v>42</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5819,10 +5843,10 @@
         <v>42</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5839,10 +5863,10 @@
         <v>42</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5859,7 +5883,7 @@
         <v>42</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5879,7 +5903,7 @@
         <v>42</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5899,7 +5923,7 @@
         <v>42</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5916,10 +5940,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5936,10 +5960,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5956,10 +5980,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5976,10 +6000,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5999,7 +6023,7 @@
         <v>90</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6019,7 +6043,7 @@
         <v>90</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6039,7 +6063,7 @@
         <v>90</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6056,10 +6080,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6076,10 +6100,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6096,10 +6120,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6116,10 +6140,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6139,7 +6163,7 @@
         <v>93</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>5</v>
@@ -6159,7 +6183,7 @@
         <v>93</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>5</v>
@@ -6179,7 +6203,7 @@
         <v>93</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>5</v>
@@ -6199,7 +6223,7 @@
         <v>93</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>5</v>
@@ -6219,9 +6243,89 @@
         <v>93</v>
       </c>
       <c r="E221" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E225" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F221" s="1" t="s">
+      <c r="F225" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/DJM02N.xlsx
+++ b/E/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="462">
   <si>
     <t/>
   </si>
@@ -883,24 +883,12 @@
     <t>BLENDS PRPL.EDT 20'S</t>
   </si>
   <si>
-    <t>20136325</t>
-  </si>
-  <si>
-    <t>BLENDS BLSM.EDT 20'S</t>
-  </si>
-  <si>
     <t>20136326</t>
   </si>
   <si>
     <t>BLENDS SMMR.EDT 20'S</t>
   </si>
   <si>
-    <t>20138346</t>
-  </si>
-  <si>
-    <t>BLENDS RICH.EDT 20'S</t>
-  </si>
-  <si>
     <t>20139349</t>
   </si>
   <si>
@@ -1177,12 +1165,6 @@
     <t>WIN KRETEK BERRY 12S</t>
   </si>
   <si>
-    <t>20136051</t>
-  </si>
-  <si>
-    <t>WIN KRT NANGKA 12'S</t>
-  </si>
-  <si>
     <t>20108797</t>
   </si>
   <si>
@@ -1219,12 +1201,6 @@
     <t>ESSE BERRY POP 16'S</t>
   </si>
   <si>
-    <t>20114735</t>
-  </si>
-  <si>
-    <t>ESSE BERRY POP 12'S</t>
-  </si>
-  <si>
     <t>20093678</t>
   </si>
   <si>
@@ -1247,12 +1223,6 @@
   </si>
   <si>
     <t>JUARA  APEL 12S</t>
-  </si>
-  <si>
-    <t>20130786</t>
-  </si>
-  <si>
-    <t>JUARA  MNGGA 12S</t>
   </si>
   <si>
     <t>20095302</t>
@@ -1819,7 +1789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F225"/>
+  <dimension ref="A1:F220"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4566,7 +4536,7 @@
         <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4586,7 +4556,7 @@
         <v>15</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4606,7 +4576,7 @@
         <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4623,10 +4593,10 @@
         <v>33</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4643,10 +4613,10 @@
         <v>33</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4686,7 +4656,7 @@
         <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4706,7 +4676,7 @@
         <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4746,7 +4716,7 @@
         <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4766,7 +4736,7 @@
         <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4866,7 +4836,7 @@
         <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4926,7 +4896,7 @@
         <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4943,7 +4913,7 @@
         <v>33</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>9</v>
@@ -4963,7 +4933,7 @@
         <v>33</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>9</v>
@@ -5026,7 +4996,7 @@
         <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5046,7 +5016,7 @@
         <v>21</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5103,7 +5073,7 @@
         <v>33</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5120,10 +5090,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5140,10 +5110,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5163,7 +5133,7 @@
         <v>36</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5183,7 +5153,7 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5203,7 +5173,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5223,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5243,7 +5213,7 @@
         <v>36</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5263,7 +5233,7 @@
         <v>36</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5283,7 +5253,7 @@
         <v>36</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5303,7 +5273,7 @@
         <v>36</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5323,10 +5293,10 @@
         <v>36</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5343,7 +5313,7 @@
         <v>36</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5363,7 +5333,7 @@
         <v>36</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>9</v>
@@ -5383,7 +5353,7 @@
         <v>36</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5400,13 +5370,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5420,10 +5390,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5443,7 +5413,7 @@
         <v>39</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5463,7 +5433,7 @@
         <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5483,7 +5453,7 @@
         <v>39</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5503,7 +5473,7 @@
         <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5523,7 +5493,7 @@
         <v>39</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5543,7 +5513,7 @@
         <v>39</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5563,7 +5533,7 @@
         <v>39</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5583,7 +5553,7 @@
         <v>39</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5603,7 +5573,7 @@
         <v>39</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5623,7 +5593,7 @@
         <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5640,10 +5610,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5660,10 +5630,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5680,10 +5650,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5700,10 +5670,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5723,10 +5693,10 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5743,10 +5713,10 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5763,10 +5733,10 @@
         <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5783,7 +5753,7 @@
         <v>42</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5803,7 +5773,7 @@
         <v>42</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5823,10 +5793,10 @@
         <v>42</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5843,10 +5813,10 @@
         <v>42</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5863,10 +5833,10 @@
         <v>42</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -5883,7 +5853,7 @@
         <v>42</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5903,7 +5873,7 @@
         <v>42</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5920,10 +5890,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5940,10 +5910,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5960,10 +5930,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5980,10 +5950,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6000,10 +5970,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6023,7 +5993,7 @@
         <v>90</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6043,7 +6013,7 @@
         <v>90</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6060,10 +6030,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6080,10 +6050,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6100,10 +6070,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6120,10 +6090,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6140,10 +6110,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6163,7 +6133,7 @@
         <v>93</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>5</v>
@@ -6183,7 +6153,7 @@
         <v>93</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>5</v>
@@ -6203,7 +6173,7 @@
         <v>93</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>5</v>
@@ -6223,109 +6193,9 @@
         <v>93</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F221" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F222" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F223" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E224" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F224" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E225" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F225" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/DJM02N.xlsx
+++ b/E/DJM02N.xlsx
@@ -295,6 +295,42 @@
     <t>15</t>
   </si>
   <si>
+    <t>10010100</t>
+  </si>
+  <si>
+    <t>MARLBORO HPACK 20'S</t>
+  </si>
+  <si>
+    <t>20107181</t>
+  </si>
+  <si>
+    <t>MARLBORO SE 20'S</t>
+  </si>
+  <si>
+    <t>20143381</t>
+  </si>
+  <si>
+    <t>MARLBORO RED ADV20S</t>
+  </si>
+  <si>
+    <t>20143380</t>
+  </si>
+  <si>
+    <t>MARLBORO GOLD ADV20S</t>
+  </si>
+  <si>
+    <t>20107184</t>
+  </si>
+  <si>
+    <t>MARLBORO GOLD SE 20S</t>
+  </si>
+  <si>
+    <t>10010102</t>
+  </si>
+  <si>
+    <t>MARLBORO LIGHT 20'S</t>
+  </si>
+  <si>
     <t>20043389</t>
   </si>
   <si>
@@ -343,16 +379,91 @@
     <t>FILTER MOTION 20'S</t>
   </si>
   <si>
-    <t>20143381</t>
-  </si>
-  <si>
-    <t>MARLBORO RED ADV20S</t>
-  </si>
-  <si>
-    <t>20143380</t>
-  </si>
-  <si>
-    <t>MARLBORO GOLD ADV20S</t>
+    <t>20129762</t>
+  </si>
+  <si>
+    <t>TWIZZ R/F RYL CR 12S</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10010090</t>
+  </si>
+  <si>
+    <t>SAMPOERNA MLD 12/MRH</t>
+  </si>
+  <si>
+    <t>10010091</t>
+  </si>
+  <si>
+    <t>SAMPOERNA MILD 16'S</t>
+  </si>
+  <si>
+    <t>20135439</t>
+  </si>
+  <si>
+    <t>SAMPOERNA MLD CLS16S</t>
+  </si>
+  <si>
+    <t>20131370</t>
+  </si>
+  <si>
+    <t>SAMPOERNA ROYAL 16'S</t>
+  </si>
+  <si>
+    <t>20079512</t>
+  </si>
+  <si>
+    <t>SMPOERNA MNTHL.BR 16</t>
+  </si>
+  <si>
+    <t>20095217</t>
+  </si>
+  <si>
+    <t>SMPOERNA TRPCAL 16'S</t>
+  </si>
+  <si>
+    <t>20064088</t>
+  </si>
+  <si>
+    <t>SMPOERNA AVOLTN 20'S</t>
+  </si>
+  <si>
+    <t>20064089</t>
+  </si>
+  <si>
+    <t>SMPOERNA AVLT MNT 20</t>
+  </si>
+  <si>
+    <t>20138598</t>
+  </si>
+  <si>
+    <t>SMPOERN AVL RY.BRS20</t>
+  </si>
+  <si>
+    <t>20135544</t>
+  </si>
+  <si>
+    <t>MARLBORO TRPCL BS16S</t>
+  </si>
+  <si>
+    <t>20137571</t>
+  </si>
+  <si>
+    <t>TWIZZ PRIME 16'S</t>
+  </si>
+  <si>
+    <t>20139762</t>
+  </si>
+  <si>
+    <t>TWIZZ PRM ROYAL 16S</t>
+  </si>
+  <si>
+    <t>20139763</t>
+  </si>
+  <si>
+    <t>TWIZZ PRM TRPCL 16S</t>
   </si>
   <si>
     <t>20123283</t>
@@ -361,121 +472,10 @@
     <t>TWIZZ R/F RYL CR 16S</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
     <t>20123284</t>
   </si>
   <si>
     <t>TWIZZ YELLOW CR 16'S</t>
-  </si>
-  <si>
-    <t>20129762</t>
-  </si>
-  <si>
-    <t>TWIZZ R/F RYL CR 12S</t>
-  </si>
-  <si>
-    <t>20139762</t>
-  </si>
-  <si>
-    <t>TWIZZ PRM ROYAL 16S</t>
-  </si>
-  <si>
-    <t>20139763</t>
-  </si>
-  <si>
-    <t>TWIZZ PRM TRPCL 16S</t>
-  </si>
-  <si>
-    <t>10010090</t>
-  </si>
-  <si>
-    <t>SAMPOERNA MLD 12/MRH</t>
-  </si>
-  <si>
-    <t>10010091</t>
-  </si>
-  <si>
-    <t>SAMPOERNA MILD 16'S</t>
-  </si>
-  <si>
-    <t>20135439</t>
-  </si>
-  <si>
-    <t>SAMPOERNA MLD CLS16S</t>
-  </si>
-  <si>
-    <t>20131370</t>
-  </si>
-  <si>
-    <t>SAMPOERNA ROYAL 16'S</t>
-  </si>
-  <si>
-    <t>20079512</t>
-  </si>
-  <si>
-    <t>SMPOERNA MNTHL.BR 16</t>
-  </si>
-  <si>
-    <t>20095217</t>
-  </si>
-  <si>
-    <t>SMPOERNA TRPCAL 16'S</t>
-  </si>
-  <si>
-    <t>20064088</t>
-  </si>
-  <si>
-    <t>SMPOERNA AVOLTN 20'S</t>
-  </si>
-  <si>
-    <t>20064089</t>
-  </si>
-  <si>
-    <t>SMPOERNA AVLT MNT 20</t>
-  </si>
-  <si>
-    <t>20138598</t>
-  </si>
-  <si>
-    <t>SMPOERN AVL RY.BRS20</t>
-  </si>
-  <si>
-    <t>10010100</t>
-  </si>
-  <si>
-    <t>MARLBORO HPACK 20'S</t>
-  </si>
-  <si>
-    <t>20107181</t>
-  </si>
-  <si>
-    <t>MARLBORO SE 20'S</t>
-  </si>
-  <si>
-    <t>10010102</t>
-  </si>
-  <si>
-    <t>MARLBORO LIGHT 20'S</t>
-  </si>
-  <si>
-    <t>20107184</t>
-  </si>
-  <si>
-    <t>MARLBORO GOLD SE 20S</t>
-  </si>
-  <si>
-    <t>20135544</t>
-  </si>
-  <si>
-    <t>MARLBORO TRPCL BS16S</t>
-  </si>
-  <si>
-    <t>20137571</t>
-  </si>
-  <si>
-    <t>TWIZZ PRIME 16'S</t>
   </si>
   <si>
     <t>20033460</t>
@@ -2576,7 +2576,7 @@
         <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2616,7 +2616,7 @@
         <v>12</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2636,7 +2636,7 @@
         <v>15</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2676,7 +2676,7 @@
         <v>21</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2696,7 +2696,7 @@
         <v>24</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2716,7 +2716,7 @@
         <v>27</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2736,7 +2736,7 @@
         <v>30</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2756,7 +2756,7 @@
         <v>33</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2776,15 +2776,15 @@
         <v>36</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>116</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2796,15 +2796,15 @@
         <v>39</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>116</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2816,15 +2816,15 @@
         <v>42</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>116</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2836,15 +2836,15 @@
         <v>90</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2856,7 +2856,7 @@
         <v>93</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,7 +3056,7 @@
         <v>33</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3136,7 +3136,7 @@
         <v>90</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3156,7 +3156,7 @@
         <v>93</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3796,7 +3796,7 @@
         <v>24</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -5553,7 +5553,7 @@
         <v>39</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5573,7 +5573,7 @@
         <v>39</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5593,7 +5593,7 @@
         <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
